--- a/escola-de-obra/02-curso-piloto/kit/planilha/planilha-fissuras.xlsx
+++ b/escola-de-obra/02-curso-piloto/kit/planilha/planilha-fissuras.xlsx
@@ -813,7 +813,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Abertura de referência (NBR 6118, Tab. 13.4 — CAA II/III). Ajustar à classe de agressividade. [VALIDAR B1]</t>
+          <t>Abertura de referência (NBR 6118:2023, Tab. 13.4 — CAA II/III). Ajustar à classe de agressividade. [VALIDAR B1]</t>
         </is>
       </c>
     </row>
